--- a/dataset_t6_grouped/results2/G5/G5_T6588_W0053F0002T0006Z000C1N9_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6588_W0053F0002T0006Z000C1N9_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>6.792689126765394</v>
+        <v>1.103811983099376</v>
       </c>
       <c r="D2" t="n">
-        <v>12.83653122399293</v>
+        <v>2.085936323898852</v>
       </c>
       <c r="E2" t="n">
-        <v>1.203098299677416</v>
+        <v>0.19550347369758</v>
       </c>
       <c r="F2" t="n">
-        <v>4.5902224079842</v>
+        <v>0.7459111412974325</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>4.386492527410563</v>
+        <v>0.7128050357042165</v>
       </c>
       <c r="D3" t="n">
-        <v>3.656086408024532</v>
+        <v>0.5941140413039864</v>
       </c>
       <c r="E3" t="n">
-        <v>1.203098299677416</v>
+        <v>0.19550347369758</v>
       </c>
       <c r="F3" t="n">
-        <v>4.5902224079842</v>
+        <v>0.7459111412974325</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
